--- a/data.mn/public/datasets/imported-vehicles-by-type.xlsx
+++ b/data.mn/public/datasets/imported-vehicles-by-type.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,11 @@
   </sheetPr>
   <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -440,11 +445,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13114</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="3">
@@ -453,11 +458,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2791</v>
+        <v>13114</v>
       </c>
     </row>
     <row r="4">
@@ -479,11 +484,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38241</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="6">
@@ -492,11 +497,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3172</v>
+        <v>17733</v>
       </c>
     </row>
     <row r="7">
@@ -505,11 +510,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17733</v>
+        <v>38241</v>
       </c>
     </row>
     <row r="8">
@@ -531,11 +536,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11451</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="10">
@@ -544,11 +549,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4557</v>
+        <v>11451</v>
       </c>
     </row>
     <row r="11">
@@ -557,11 +562,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26066</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="12">
@@ -583,11 +588,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1634</v>
+        <v>26066</v>
       </c>
     </row>
     <row r="14">
@@ -596,11 +601,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56805</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="15">
@@ -622,11 +627,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2807</v>
+        <v>56805</v>
       </c>
     </row>
     <row r="17">
@@ -635,11 +640,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45748</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="18">
@@ -648,11 +653,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2432</v>
+        <v>22438</v>
       </c>
     </row>
     <row r="19">
@@ -661,11 +666,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22438</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="20">
@@ -687,11 +692,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44680</v>
+        <v>17995</v>
       </c>
     </row>
     <row r="22">
@@ -700,11 +705,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17995</v>
+        <v>44680</v>
       </c>
     </row>
     <row r="23">
@@ -726,11 +731,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41246</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="25">
@@ -739,11 +744,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12500</v>
+        <v>41246</v>
       </c>
     </row>
     <row r="26">
@@ -752,11 +757,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37086</v>
+        <v>870</v>
       </c>
     </row>
     <row r="27">
@@ -765,11 +770,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>870</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="28">
@@ -778,11 +783,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7675</v>
+        <v>37086</v>
       </c>
     </row>
     <row r="29">
@@ -791,11 +796,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6836</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30">
@@ -804,11 +809,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37735</v>
+        <v>6836</v>
       </c>
     </row>
     <row r="31">
@@ -817,11 +822,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>37735</v>
       </c>
     </row>
     <row r="32">
@@ -869,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64039</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="36">
@@ -882,11 +887,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1363</v>
+        <v>22256</v>
       </c>
     </row>
     <row r="37">
@@ -895,11 +900,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22256</v>
+        <v>64039</v>
       </c>
     </row>
     <row r="38">
@@ -908,11 +913,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69472</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="39">
@@ -921,11 +926,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1543</v>
+        <v>23050</v>
       </c>
     </row>
     <row r="40">
@@ -934,11 +939,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23050</v>
+        <v>69472</v>
       </c>
     </row>
     <row r="41">
@@ -947,11 +952,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>53087</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="42">
@@ -960,11 +965,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1359</v>
+        <v>20982</v>
       </c>
     </row>
     <row r="43">
@@ -973,11 +978,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>20982</v>
+        <v>53087</v>
       </c>
     </row>
     <row r="44">
@@ -1025,11 +1030,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>65612</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="48">
@@ -1038,11 +1043,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1082</v>
+        <v>22369</v>
       </c>
     </row>
     <row r="49">
@@ -1051,11 +1056,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22369</v>
+        <v>65612</v>
       </c>
     </row>
     <row r="50">
@@ -1064,11 +1069,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>21361</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="51">
@@ -1077,11 +1082,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73556</v>
+        <v>21363</v>
       </c>
     </row>
     <row r="52">
@@ -1090,11 +1095,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1731</v>
+        <v>73556</v>
       </c>
     </row>
     <row r="53">
@@ -1103,11 +1108,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>28822</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="54">
@@ -1116,11 +1121,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>123089</v>
+        <v>28822</v>
       </c>
     </row>
     <row r="55">
@@ -1129,11 +1134,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2383</v>
+        <v>123089</v>
       </c>
     </row>
     <row r="56">
@@ -1142,11 +1147,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Freight Vehicles</t>
+          <t>Buses &amp; Large Vehicles</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20965</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="57">
@@ -1155,11 +1160,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Passenger Cars</t>
+          <t>Freight Vehicles</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>90151</v>
+        <v>21031</v>
       </c>
     </row>
     <row r="58">
@@ -1168,11 +1173,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Buses &amp; Large Vehicles</t>
+          <t>Passenger Cars</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1175</v>
+        <v>90406</v>
       </c>
     </row>
   </sheetData>
@@ -1188,21 +1193,26 @@
   </sheetPr>
   <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>он</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>vehicle_type</t>
+          <t>төрөл</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>тоо</t>
         </is>
       </c>
     </row>
@@ -1212,11 +1222,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13114</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="3">
@@ -1225,11 +1235,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2791</v>
+        <v>13114</v>
       </c>
     </row>
     <row r="4">
@@ -1251,11 +1261,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38241</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="6">
@@ -1264,11 +1274,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3172</v>
+        <v>17733</v>
       </c>
     </row>
     <row r="7">
@@ -1277,11 +1287,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17733</v>
+        <v>38241</v>
       </c>
     </row>
     <row r="8">
@@ -1303,11 +1313,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11451</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="10">
@@ -1316,11 +1326,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4557</v>
+        <v>11451</v>
       </c>
     </row>
     <row r="11">
@@ -1329,11 +1339,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26066</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="12">
@@ -1355,11 +1365,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1634</v>
+        <v>26066</v>
       </c>
     </row>
     <row r="14">
@@ -1368,11 +1378,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56805</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="15">
@@ -1394,11 +1404,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2807</v>
+        <v>56805</v>
       </c>
     </row>
     <row r="17">
@@ -1407,11 +1417,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45748</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="18">
@@ -1420,11 +1430,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2432</v>
+        <v>22438</v>
       </c>
     </row>
     <row r="19">
@@ -1433,11 +1443,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22438</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="20">
@@ -1459,11 +1469,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44680</v>
+        <v>17995</v>
       </c>
     </row>
     <row r="22">
@@ -1472,11 +1482,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17995</v>
+        <v>44680</v>
       </c>
     </row>
     <row r="23">
@@ -1498,11 +1508,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41246</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="25">
@@ -1511,11 +1521,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12500</v>
+        <v>41246</v>
       </c>
     </row>
     <row r="26">
@@ -1524,11 +1534,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37086</v>
+        <v>870</v>
       </c>
     </row>
     <row r="27">
@@ -1537,11 +1547,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>870</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="28">
@@ -1550,11 +1560,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7675</v>
+        <v>37086</v>
       </c>
     </row>
     <row r="29">
@@ -1563,11 +1573,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6836</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30">
@@ -1576,11 +1586,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37735</v>
+        <v>6836</v>
       </c>
     </row>
     <row r="31">
@@ -1589,11 +1599,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>37735</v>
       </c>
     </row>
     <row r="32">
@@ -1641,11 +1651,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64039</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="36">
@@ -1654,11 +1664,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1363</v>
+        <v>22256</v>
       </c>
     </row>
     <row r="37">
@@ -1667,11 +1677,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22256</v>
+        <v>64039</v>
       </c>
     </row>
     <row r="38">
@@ -1680,11 +1690,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69472</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="39">
@@ -1693,11 +1703,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1543</v>
+        <v>23050</v>
       </c>
     </row>
     <row r="40">
@@ -1706,11 +1716,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23050</v>
+        <v>69472</v>
       </c>
     </row>
     <row r="41">
@@ -1719,11 +1729,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>53087</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="42">
@@ -1732,11 +1742,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1359</v>
+        <v>20982</v>
       </c>
     </row>
     <row r="43">
@@ -1745,11 +1755,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>20982</v>
+        <v>53087</v>
       </c>
     </row>
     <row r="44">
@@ -1797,11 +1807,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>65612</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="48">
@@ -1810,11 +1820,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1082</v>
+        <v>22369</v>
       </c>
     </row>
     <row r="49">
@@ -1823,11 +1833,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22369</v>
+        <v>65612</v>
       </c>
     </row>
     <row r="50">
@@ -1836,11 +1846,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>21361</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="51">
@@ -1849,11 +1859,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73556</v>
+        <v>21363</v>
       </c>
     </row>
     <row r="52">
@@ -1862,11 +1872,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1731</v>
+        <v>73556</v>
       </c>
     </row>
     <row r="53">
@@ -1875,11 +1885,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>28822</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="54">
@@ -1888,11 +1898,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>123089</v>
+        <v>28822</v>
       </c>
     </row>
     <row r="55">
@@ -1901,11 +1911,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2383</v>
+        <v>123089</v>
       </c>
     </row>
     <row r="56">
@@ -1914,11 +1924,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ачааны тээврийн хэрэгсэл</t>
+          <t>Автобус, том тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20965</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="57">
@@ -1927,11 +1937,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Суудлын автомашин</t>
+          <t>Ачааны тээврийн хэрэгсэл</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>90151</v>
+        <v>21031</v>
       </c>
     </row>
     <row r="58">
@@ -1940,11 +1950,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Автобус, том тээврийн хэрэгсэл</t>
+          <t>Суудлын автомашин</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1175</v>
+        <v>90406</v>
       </c>
     </row>
   </sheetData>
